--- a/data/trans_camb/IP19C01-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP19C01-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 24,58</t>
+          <t>-6,56; 23,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-21,38; 17,15</t>
+          <t>-21,18; 18,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,4; 30,97</t>
+          <t>-18,22; 30,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 20,12</t>
+          <t>-12,79; 19,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,56; 16,17</t>
+          <t>-17,17; 16,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 30,06</t>
+          <t>-3,27; 28,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 17,18</t>
+          <t>-4,75; 17,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,74; 12,07</t>
+          <t>-14,61; 12,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 24,93</t>
+          <t>-4,54; 25,11</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 45,09</t>
+          <t>-9,05; 41,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-31,55; 29,1</t>
+          <t>-30,9; 32,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-24,8; 53,06</t>
+          <t>-25,89; 52,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,42; 33,34</t>
+          <t>-16,38; 30,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,84; 25,39</t>
+          <t>-23,33; 26,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 50,64</t>
+          <t>-4,01; 47,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 28,95</t>
+          <t>-6,34; 28,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-20,4; 19,73</t>
+          <t>-19,86; 19,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 40,87</t>
+          <t>-6,06; 40,4</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 13,19</t>
+          <t>-0,62; 13,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 16,38</t>
+          <t>3,06; 16,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,2; 27,14</t>
+          <t>14,17; 27,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 9,19</t>
+          <t>-3,61; 8,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 13,74</t>
+          <t>0,97; 13,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 16,0</t>
+          <t>1,77; 15,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 9,12</t>
+          <t>-0,25; 9,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 12,92</t>
+          <t>3,69; 12,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,13; 19,19</t>
+          <t>9,83; 19,2</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 22,43</t>
+          <t>-0,95; 23,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,08; 27,42</t>
+          <t>4,54; 27,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,16; 46,29</t>
+          <t>21,36; 46,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 13,55</t>
+          <t>-4,68; 13,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 20,62</t>
+          <t>1,36; 19,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,66; 23,99</t>
+          <t>2,33; 22,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 14,1</t>
+          <t>-0,37; 14,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,51; 19,96</t>
+          <t>5,49; 20,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,55; 29,65</t>
+          <t>13,94; 29,49</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,63; 13,24</t>
+          <t>-9,7; 13,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 13,06</t>
+          <t>-8,59; 12,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 12,48</t>
+          <t>-9,86; 10,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 21,35</t>
+          <t>0,69; 22,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 9,01</t>
+          <t>-13,92; 10,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,02; 24,26</t>
+          <t>3,65; 23,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 13,85</t>
+          <t>-1,65; 13,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 7,53</t>
+          <t>-8,1; 7,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 15,19</t>
+          <t>0,83; 15,58</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 19,04</t>
+          <t>-11,89; 19,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 18,87</t>
+          <t>-10,56; 18,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 18,07</t>
+          <t>-12,16; 15,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 31,59</t>
+          <t>1,0; 34,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-17,85; 13,33</t>
+          <t>-17,57; 15,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,33; 37,56</t>
+          <t>4,7; 35,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 19,79</t>
+          <t>-2,06; 19,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 10,7</t>
+          <t>-10,22; 10,94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,76; 21,63</t>
+          <t>1,02; 22,36</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 11,17</t>
+          <t>0,94; 11,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,01; 13,36</t>
+          <t>1,86; 13,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,99; 20,71</t>
+          <t>10,16; 20,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 9,78</t>
+          <t>-0,4; 9,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 9,83</t>
+          <t>-0,88; 9,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,87; 16,33</t>
+          <t>5,54; 16,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 9,07</t>
+          <t>1,05; 8,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 9,7</t>
+          <t>2,0; 9,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,37; 16,91</t>
+          <t>9,47; 17,08</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,7</t>
+          <t>1,38; 17,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,95; 21,28</t>
+          <t>2,62; 21,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,47; 32,73</t>
+          <t>14,49; 32,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 14,23</t>
+          <t>-0,52; 14,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 14,53</t>
+          <t>-1,19; 13,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,84; 23,68</t>
+          <t>7,55; 23,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,91; 13,51</t>
+          <t>1,47; 13,1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,11; 14,59</t>
+          <t>2,83; 14,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,38; 25,29</t>
+          <t>13,51; 25,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C01-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP19C01-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 23,35</t>
+          <t>-7,34; 24,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-21,18; 18,76</t>
+          <t>-23,61; 15,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,22; 30,46</t>
+          <t>-18,93; 28,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 19,04</t>
+          <t>-12,03; 20,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,17; 16,92</t>
+          <t>-18,51; 17,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 28,85</t>
+          <t>-3,68; 30,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 17,2</t>
+          <t>-5,5; 17,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,61; 12,42</t>
+          <t>-12,94; 11,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 25,11</t>
+          <t>-4,76; 25,22</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 41,46</t>
+          <t>-9,83; 44,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,9; 32,21</t>
+          <t>-34,12; 25,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,89; 52,09</t>
+          <t>-25,45; 49,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,38; 30,88</t>
+          <t>-15,31; 33,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,33; 26,57</t>
+          <t>-24,53; 28,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 47,65</t>
+          <t>-3,92; 52,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 28,4</t>
+          <t>-7,17; 28,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-19,86; 19,51</t>
+          <t>-18,45; 19,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 40,4</t>
+          <t>-6,52; 40,31</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 13,51</t>
+          <t>-1,16; 14,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 16,5</t>
+          <t>2,33; 16,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,17; 27,25</t>
+          <t>14,57; 27,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 8,73</t>
+          <t>-4,11; 8,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 13,25</t>
+          <t>1,39; 13,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 15,48</t>
+          <t>2,08; 15,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 9,51</t>
+          <t>-1,12; 8,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,69; 12,88</t>
+          <t>3,14; 13,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,83; 19,2</t>
+          <t>9,39; 19,16</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 23,08</t>
+          <t>-1,67; 24,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,54; 27,49</t>
+          <t>3,68; 27,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,36; 46,22</t>
+          <t>21,55; 46,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 13,06</t>
+          <t>-5,75; 13,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 19,76</t>
+          <t>1,96; 20,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 22,91</t>
+          <t>2,49; 23,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 14,61</t>
+          <t>-1,61; 13,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,49; 20,3</t>
+          <t>4,57; 20,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,94; 29,49</t>
+          <t>13,12; 29,42</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 13,83</t>
+          <t>-8,76; 13,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 12,92</t>
+          <t>-7,51; 13,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 10,85</t>
+          <t>-9,46; 12,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 22,29</t>
+          <t>0,5; 20,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 10,11</t>
+          <t>-14,1; 9,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,65; 23,68</t>
+          <t>4,15; 24,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 13,83</t>
+          <t>-1,27; 13,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 7,69</t>
+          <t>-7,18; 8,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 15,58</t>
+          <t>1,14; 15,65</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 19,93</t>
+          <t>-10,58; 19,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 18,55</t>
+          <t>-8,99; 20,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 15,32</t>
+          <t>-11,69; 17,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 34,3</t>
+          <t>0,65; 31,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-17,57; 15,48</t>
+          <t>-17,56; 14,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,7; 35,91</t>
+          <t>5,03; 36,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 19,47</t>
+          <t>-1,44; 19,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 10,94</t>
+          <t>-9,22; 11,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,02; 22,36</t>
+          <t>1,56; 22,39</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 11,22</t>
+          <t>0,74; 11,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,86; 13,3</t>
+          <t>1,68; 13,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,16; 20,82</t>
+          <t>9,77; 20,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 9,88</t>
+          <t>-0,91; 9,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 9,63</t>
+          <t>-1,17; 9,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,54; 16,09</t>
+          <t>5,61; 16,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 8,78</t>
+          <t>1,54; 9,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,0; 9,95</t>
+          <t>2,4; 10,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,47; 17,08</t>
+          <t>9,6; 17,11</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,38; 17,72</t>
+          <t>1,16; 18,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,62; 21,13</t>
+          <t>2,48; 20,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,49; 32,87</t>
+          <t>14,21; 33,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 14,62</t>
+          <t>-1,24; 14,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 13,99</t>
+          <t>-1,58; 14,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,55; 23,58</t>
+          <t>7,54; 23,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,47; 13,1</t>
+          <t>2,15; 14,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,83; 14,96</t>
+          <t>3,39; 15,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,51; 25,81</t>
+          <t>13,78; 25,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C01-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP19C01-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,63</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,06</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14,16</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>9,08</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-1,35</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11,5</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,63</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,06</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,5</t>
+          <t>17,79</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12,79</t>
+          <t>16,06</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 24,69</t>
+          <t>-13,26; 20,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-23,61; 15,57</t>
+          <t>-18,56; 16,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,93; 28,9</t>
+          <t>-4,74; 29,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 20,82</t>
+          <t>-6,06; 24,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,51; 17,59</t>
+          <t>-21,38; 17,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 30,89</t>
+          <t>0,93; 33,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 17,54</t>
+          <t>-4,45; 17,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,94; 11,92</t>
+          <t>-14,74; 12,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 25,22</t>
+          <t>3,55; 27,76</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5,15%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-1,5%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20,08%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>14,04%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-2,09%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>17,79%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,15%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-1,5%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>23,8%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 44,68</t>
+          <t>-16,42; 33,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-34,12; 25,96</t>
+          <t>-23,84; 25,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,45; 49,0</t>
+          <t>-5,85; 49,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 33,54</t>
+          <t>-8,21; 45,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,53; 28,04</t>
+          <t>-31,55; 29,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 52,72</t>
+          <t>1,4; 61,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 28,35</t>
+          <t>-5,96; 28,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,45; 19,13</t>
+          <t>-20,4; 19,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 40,31</t>
+          <t>5,46; 46,16</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,55</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7,41</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9,41</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>6,29</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>9,56</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>20,92</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,55</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,41</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,17</t>
+          <t>20,53</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14,69</t>
+          <t>14,7</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 14,06</t>
+          <t>-4,4; 9,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 16,23</t>
+          <t>1,04; 13,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,57; 27,34</t>
+          <t>2,99; 16,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 8,96</t>
+          <t>-1,09; 13,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 13,54</t>
+          <t>2,61; 16,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 15,78</t>
+          <t>13,96; 26,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 8,76</t>
+          <t>-0,82; 9,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,14; 13,05</t>
+          <t>3,82; 12,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,39; 19,16</t>
+          <t>10,11; 19,12</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10,45%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13,27%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>9,96%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>15,14%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>33,13%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,45%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 24,11</t>
+          <t>-5,98; 13,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,68; 27,55</t>
+          <t>1,37; 20,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,55; 46,28</t>
+          <t>4,08; 24,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 13,36</t>
+          <t>-1,42; 22,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 20,23</t>
+          <t>4,08; 27,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,49; 23,24</t>
+          <t>20,86; 45,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 13,46</t>
+          <t>-1,22; 14,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 20,3</t>
+          <t>5,51; 19,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,12; 29,42</t>
+          <t>14,59; 29,76</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>10,88</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-2,41</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>14,11</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>1,99</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2,49</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,82</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>10,88</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-2,41</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,02</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8,19</t>
+          <t>7,97</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 13,43</t>
+          <t>-0,04; 21,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 13,91</t>
+          <t>-14,12; 9,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 12,2</t>
+          <t>5,18; 24,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 20,84</t>
+          <t>-9,63; 13,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,1; 9,82</t>
+          <t>-8,19; 13,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,15; 24,63</t>
+          <t>-9,83; 12,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 13,49</t>
+          <t>-1,12; 13,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 8,29</t>
+          <t>-8,12; 7,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 15,65</t>
+          <t>0,35; 14,45</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>14,81%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-3,28%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19,2%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>2,61%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>3,27%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>14,81%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-3,28%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,65%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 19,55</t>
+          <t>-0,06; 31,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 20,74</t>
+          <t>-17,85; 13,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,69; 17,37</t>
+          <t>6,75; 38,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,65; 31,38</t>
+          <t>-11,62; 19,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-17,56; 14,67</t>
+          <t>-9,91; 18,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,03; 36,76</t>
+          <t>-11,97; 17,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 19,15</t>
+          <t>-1,35; 19,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 11,86</t>
+          <t>-10,16; 10,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,56; 22,39</t>
+          <t>0,49; 21,06</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4,59</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4,54</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11,17</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>5,96</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>7,4</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>15,5</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,59</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4,54</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,03</t>
+          <t>15,69</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13,27</t>
+          <t>13,42</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 11,59</t>
+          <t>-1,05; 9,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,68; 13,02</t>
+          <t>-1,1; 9,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,77; 20,68</t>
+          <t>6,09; 16,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 9,85</t>
+          <t>-0,07; 11,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 9,67</t>
+          <t>2,01; 13,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,61; 16,28</t>
+          <t>10,6; 21,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,54; 9,44</t>
+          <t>1,33; 9,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,4; 10,07</t>
+          <t>2,2; 9,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,6; 17,11</t>
+          <t>9,77; 17,07</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>6,43%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>6,36%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>15,65%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>9,0%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>11,19%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>23,43%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>6,43%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,16; 18,8</t>
+          <t>-1,45; 14,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,48; 20,44</t>
+          <t>-1,2; 14,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,21; 33,0</t>
+          <t>8,16; 24,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 14,57</t>
+          <t>0,0; 17,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 14,27</t>
+          <t>2,95; 21,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,54; 23,78</t>
+          <t>15,44; 33,75</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,15; 14,41</t>
+          <t>1,91; 13,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,39; 15,07</t>
+          <t>3,11; 14,59</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,78; 25,87</t>
+          <t>13,74; 25,42</t>
         </is>
       </c>
     </row>
